--- a/docs/정책결정관리서.xlsx
+++ b/docs/정책결정관리서.xlsx
@@ -83,7 +83,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -105,11 +105,55 @@
         <color rgb="00CFE3F0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CFE3F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CFE3F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CFE3F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CFE3F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CFE3F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CFE3F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CFE3F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CFE3F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -129,6 +173,8 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -494,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -518,9 +564,11 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>v1</t>
-        </is>
-      </c>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="n"/>
+      <c r="D2" s="8" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -533,6 +581,8 @@
           <t>2026-06-30</t>
         </is>
       </c>
+      <c r="C3" s="7" t="n"/>
+      <c r="D3" s="8" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -542,9 +592,11 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>최초 작성 — 디자인·추천·개인화·계정·인프라·날씨·안정화 핵심 결정 19건(DEC-01~19)</t>
-        </is>
-      </c>
+          <t>DEC-20 추가 — 추천 API 보호(JWT 검증 + 계정별 일일 상한)</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="8" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -983,6 +1035,28 @@
       <c r="D24" s="5" t="inlineStr">
         <is>
           <t>관리 일원화</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>DEC-20</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>추천 API 보호</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Vercel 추천 함수(/api/outfit·/api/shop)에 백엔드와 동일 JWT_SECRET으로 토큰 검증 + 계정별 일일 상한(outfit 50회·shop 600회)</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>UI 로그인만으론 직접 호출로 우회 가능 — LLM·네이버 API 비용 어뷰징 차단</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1134,6 +1208,23 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>DEC-20 추가 — 추천 API JWT 검증 + 계정별 일일 호출 상한</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:C2"/>
   <mergeCells count="1">

--- a/docs/정책결정관리서.xlsx
+++ b/docs/정책결정관리서.xlsx
@@ -540,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -564,7 +564,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>v3</t>
         </is>
       </c>
       <c r="C2" s="7" t="n"/>
@@ -592,7 +592,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>DEC-20 추가 — 추천 API 보호(JWT 검증 + 계정별 일일 상한)</t>
+          <t>DEC-21~22 추가 — 색 팔레트 18색 확장, 사진 옷 등록 방식(확인 후 저장)</t>
         </is>
       </c>
       <c r="C4" s="7" t="n"/>
@@ -1057,6 +1057,50 @@
       <c r="D25" s="5" t="inlineStr">
         <is>
           <t>UI 로그인만으론 직접 호출로 우회 가능 — LLM·네이버 API 비용 어뷰징 차단</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>DEC-21</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>색 팔레트 확장</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>12색→18색(와인·민트·퍼플·오렌지·아이보리·차콜 추가). 닫힌 팔레트는 유지</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>의류 색 다양성 수용 — 유사색으로 뭉개짐 방지. 자유 색상은 색칩·추천 매칭·검색어 일관성이 깨져 배제</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>DEC-22</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>사진 옷 등록 방식</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>여러 장 동시 분석 + 한 장씩 확인·수정 후 저장(자동 저장 금지)</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>조명·각도에 따른 색 오인식 대비 — AI는 프리필, 확정은 사용자</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1225,6 +1269,23 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>DEC-21(색 팔레트 12→18 확장)·DEC-22(사진 옷 등록 — 여러 장 동시, 한 장씩 확인 후 저장) 추가</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:C2"/>
   <mergeCells count="1">

--- a/docs/정책결정관리서.xlsx
+++ b/docs/정책결정관리서.xlsx
@@ -540,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -564,7 +564,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>v3</t>
+          <t>v4</t>
         </is>
       </c>
       <c r="C2" s="7" t="n"/>
@@ -592,7 +592,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>DEC-21~22 추가 — 색 팔레트 18색 확장, 사진 옷 등록 방식(확인 후 저장)</t>
+          <t>DEC-23 추가 — 상황별 복장 규칙(운동=운동복·운동화 자동 강제)</t>
         </is>
       </c>
       <c r="C4" s="7" t="n"/>
@@ -1101,6 +1101,28 @@
       <c r="D27" s="5" t="inlineStr">
         <is>
           <t>조명·각도에 따른 색 오인식 대비 — AI는 프리필, 확정은 사용자</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>DEC-23</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>상황별 복장 규칙</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>추천 로직이 상황별 복장을 자동 강제 — 운동이면 운동복(기능성 티·트레이닝 하의·바람막이)·운동화만, 출근·데이트에 트레이닝복 금지. 프롬프트+룰 폴백 모두 적용</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>운동에 자켓·캐주얼 스니커즈가 추천되는 문제 — 상황별 설정 UI(설정 4배 증가) 대신 자동 규칙 선택</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1286,6 +1308,23 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>DEC-23 추가 — 상황별 복장 규칙: 운동이면 운동복·운동화만(프롬프트+룰 폴백), 설정 UI 확장 대신 자동 강제</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:C2"/>
   <mergeCells count="1">

--- a/docs/정책결정관리서.xlsx
+++ b/docs/정책결정관리서.xlsx
@@ -540,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -564,7 +564,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>v4</t>
+          <t>v5</t>
         </is>
       </c>
       <c r="C2" s="7" t="n"/>
@@ -592,7 +592,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>DEC-23 추가 — 상황별 복장 규칙(운동=운동복·운동화 자동 강제)</t>
+          <t>DEC-24 추가 — 가입 이메일 인증을 인증코드(가입 전 확인) 방식으로</t>
         </is>
       </c>
       <c r="C4" s="7" t="n"/>
@@ -1123,6 +1123,28 @@
       <c r="D28" s="5" t="inlineStr">
         <is>
           <t>운동에 자켓·캐주얼 스니커즈가 추천되는 문제 — 상황별 설정 UI(설정 4배 증가) 대신 자동 규칙 선택</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>DEC-24</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>가입 이메일 인증 방식</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>링크(가입 후 클릭) → 인증코드(가입 전 폼에서 확인, 6자리·10분·5회 제한). 인증 완료 후 계정 생성·즉시 로그인</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>오타 이메일로 계정 선점·미인증 계정 잔존 방지, 가입 직후 바로 사용 가능. 레거시 링크 인증은 기존 미인증 계정용으로 유지</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1325,6 +1347,23 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>v5</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>DEC-24 추가 — 가입 이메일 인증: 링크→인증코드(가입 전 확인·즉시 로그인)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:C2"/>
   <mergeCells count="1">

--- a/docs/정책결정관리서.xlsx
+++ b/docs/정책결정관리서.xlsx
@@ -540,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -564,7 +564,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>v5</t>
+          <t>v6</t>
         </is>
       </c>
       <c r="C2" s="7" t="n"/>
@@ -592,7 +592,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>DEC-24 추가 — 가입 이메일 인증을 인증코드(가입 전 확인) 방식으로</t>
+          <t>DEC-25 추가 — 날씨 stale 제공 + 일시 오류 1회 재시도</t>
         </is>
       </c>
       <c r="C4" s="7" t="n"/>
@@ -1145,6 +1145,28 @@
       <c r="D29" s="5" t="inlineStr">
         <is>
           <t>오타 이메일로 계정 선점·미인증 계정 잔존 방지, 가입 직후 바로 사용 가능. 레거시 링크 인증은 기존 미인증 계정용으로 유지</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>DEC-25</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>날씨 회복력 강화</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>격자별 마지막 성공 데이터를 무기한 보관(파일 영속화)해 기상청 실패 시 stale로 제공, 일시 오류는 1.5초 후 1회만 재시도(기존 무재시도 정책의 예외)</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>공공데이터포털 간헐 429·타임아웃 실측(2026-07-02) — 429 직후 재호출 성공 = 순간 튕김. 재시도 1회는 쿼터 영향 미미, 사용자 노출 장애 대폭 감소</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1364,6 +1386,23 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>v6</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>DEC-25 추가 — 날씨 서버 stale-while-revalidate + 1회 재시도(무재시도 정책 예외)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:C2"/>
   <mergeCells count="1">
